--- a/data/trans_dic/PCS12_SP_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,39; 65,29</t>
+          <t>59,35; 65,67</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,58; 68,0</t>
+          <t>61,69; 67,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,72; 64,78</t>
+          <t>57,46; 64,77</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,86; 72,25</t>
+          <t>63,5; 71,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,53; 78,0</t>
+          <t>73,47; 77,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,03; 76,17</t>
+          <t>71,26; 76,22</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,55; 75,55</t>
+          <t>69,84; 75,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77,28; 82,24</t>
+          <t>77,19; 82,32</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>68,02; 71,8</t>
+          <t>67,86; 71,9</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67,75; 71,73</t>
+          <t>67,92; 71,84</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,37; 70,13</t>
+          <t>65,4; 70,01</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,9; 77,26</t>
+          <t>72,8; 77,24</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,56; 35,99</t>
+          <t>31,39; 36,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,03; 39,43</t>
+          <t>35,06; 39,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,58; 36,62</t>
+          <t>32,5; 36,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40,85; 63,18</t>
+          <t>41,06; 65,23</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,0; 47,82</t>
+          <t>43,06; 47,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,31; 46,04</t>
+          <t>41,27; 46,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,15; 41,64</t>
+          <t>37,2; 41,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,96; 64,98</t>
+          <t>43,97; 63,68</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,52; 41,03</t>
+          <t>37,64; 41,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,68; 41,98</t>
+          <t>38,71; 41,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,5; 38,59</t>
+          <t>35,31; 38,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,59; 58,74</t>
+          <t>43,4; 58,6</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,51; 36,9</t>
+          <t>28,42; 36,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,5; 34,47</t>
+          <t>25,53; 34,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,1; 29,66</t>
+          <t>22,04; 30,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,35; 46,68</t>
+          <t>38,17; 46,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,13; 48,55</t>
+          <t>39,44; 48,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,61; 42,52</t>
+          <t>33,15; 42,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,53; 37,53</t>
+          <t>29,39; 37,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,51; 44,08</t>
+          <t>37,64; 44,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,99; 41,34</t>
+          <t>34,72; 40,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,31; 36,69</t>
+          <t>30,14; 36,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,81; 32,55</t>
+          <t>26,94; 32,52</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>39,05; 44,25</t>
+          <t>38,86; 44,34</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,98; 44,5</t>
+          <t>40,73; 44,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,22; 45,68</t>
+          <t>42,44; 46,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,12; 40,73</t>
+          <t>37,53; 40,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,38; 61,05</t>
+          <t>45,55; 61,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,36; 58,85</t>
+          <t>55,21; 58,68</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,54; 55,97</t>
+          <t>52,65; 56,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,03; 49,47</t>
+          <t>46,08; 49,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>50,77; 62,69</t>
+          <t>51,09; 62,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,6; 51,16</t>
+          <t>48,72; 51,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>47,99; 50,34</t>
+          <t>48,03; 50,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,27; 44,74</t>
+          <t>42,4; 44,67</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,92; 58,46</t>
+          <t>48,97; 58,49</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población por debajo de la mediana de la puntuación del componente de salud física (SF12)</t>
+          <t>Población por debajo de la mediana (54.994) de la puntuación del componente de salud física (SF12) (tasa de respuesta: 99,81%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>595169</t>
+          <t>595168</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>612733; 673599</t>
+          <t>612280; 677562</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>600141; 662767</t>
+          <t>601221; 659035</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>435415; 488636</t>
+          <t>433446; 488599</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>325914; 368769</t>
+          <t>324082; 366462</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>966956; 1025812</t>
+          <t>966191; 1025466</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>950233; 1019060</t>
+          <t>953302; 1019602</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>691749; 751503</t>
+          <t>694664; 753638</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>576138; 613179</t>
+          <t>575462; 613727</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1596328; 1685048</t>
+          <t>1592478; 1687401</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1566604; 1658602</t>
+          <t>1570548; 1661291</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1143347; 1226659</t>
+          <t>1143882; 1224535</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>915635; 970290</t>
+          <t>914318; 970138</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>534420; 609492</t>
+          <t>531527; 610934</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>688000; 774469</t>
+          <t>688590; 778597</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>676556; 760400</t>
+          <t>674921; 762029</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>931903; 1441493</t>
+          <t>936713; 1488324</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>682656; 759262</t>
+          <t>683709; 760617</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>726209; 809361</t>
+          <t>725513; 810901</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>738587; 827838</t>
+          <t>739616; 829901</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>981273; 1450422</t>
+          <t>981467; 1421310</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1230966; 1346291</t>
+          <t>1234878; 1347323</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1439544; 1562283</t>
+          <t>1440591; 1562730</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1443068; 1568363</t>
+          <t>1435426; 1564096</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1967549; 2651310</t>
+          <t>1958992; 2644860</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>157228; 203491</t>
+          <t>156720; 202473</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122680; 165887</t>
+          <t>122867; 165791</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120848; 162187</t>
+          <t>120521; 164202</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>247130; 300850</t>
+          <t>246001; 300571</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>186433; 231320</t>
+          <t>187883; 233104</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>149545; 194989</t>
+          <t>152038; 194003</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>162152; 206111</t>
+          <t>161382; 207210</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>246648; 289868</t>
+          <t>247487; 290458</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>359595; 424920</t>
+          <t>356904; 420836</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>284830; 344801</t>
+          <t>283238; 344793</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>293864; 356811</t>
+          <t>295259; 356452</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>508386; 576204</t>
+          <t>506007; 577299</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1342788; 1458215</t>
+          <t>1334686; 1458948</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1443841; 1562086</t>
+          <t>1451499; 1575620</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1253891; 1375707</t>
+          <t>1267604; 1378641</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1559291; 2097950</t>
+          <t>1565279; 2116264</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1870650; 1988583</t>
+          <t>1865497; 1982855</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1867351; 1989208</t>
+          <t>1871305; 1991580</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1625926; 1747467</t>
+          <t>1627701; 1747954</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1845792; 2278946</t>
+          <t>1857136; 2274429</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3234788; 3405160</t>
+          <t>3242413; 3406066</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3346668; 3510402</t>
+          <t>3349829; 3516048</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2920983; 3091655</t>
+          <t>2929660; 3086588</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3459552; 4134313</t>
+          <t>3463289; 4136424</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/PCS12_SP_R2-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/PCS12_SP_R2-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>65,7%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,54%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>59,35; 65,67</t>
+          <t>59,6; 65,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>61,69; 67,62</t>
+          <t>61,45; 67,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,46; 64,77</t>
+          <t>57,77; 64,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,5; 71,8</t>
+          <t>61,56; 69,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,47; 77,98</t>
+          <t>73,35; 78,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>71,26; 76,22</t>
+          <t>70,91; 76,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,84; 75,77</t>
+          <t>69,67; 75,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77,19; 82,32</t>
+          <t>76,52; 81,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>67,86; 71,9</t>
+          <t>68,08; 71,76</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67,92; 71,84</t>
+          <t>67,89; 71,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,4; 70,01</t>
+          <t>65,25; 69,73</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,8; 77,24</t>
+          <t>71,24; 75,73</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>44,13%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>31,39; 36,08</t>
+          <t>31,5; 36,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 39,64</t>
+          <t>34,92; 39,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32,5; 36,7</t>
+          <t>32,48; 36,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41,06; 65,23</t>
+          <t>38,97; 44,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>43,06; 47,91</t>
+          <t>42,74; 47,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,27; 46,13</t>
+          <t>41,39; 46,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,2; 41,74</t>
+          <t>37,14; 41,71</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>43,97; 63,68</t>
+          <t>44,79; 48,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,64; 41,06</t>
+          <t>37,73; 41,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38,71; 41,99</t>
+          <t>38,57; 41,84</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,31; 38,48</t>
+          <t>35,29; 38,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>43,4; 58,6</t>
+          <t>42,49; 45,71</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,61%</t>
+          <t>41,84%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>28,42; 36,72</t>
+          <t>28,87; 36,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,53; 34,46</t>
+          <t>25,58; 34,4</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,04; 30,02</t>
+          <t>21,59; 29,15</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,17; 46,64</t>
+          <t>38,05; 46,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>39,44; 48,93</t>
+          <t>39,4; 48,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33,15; 42,3</t>
+          <t>32,42; 42,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>29,39; 37,73</t>
+          <t>29,4; 37,76</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>37,64; 44,17</t>
+          <t>38,07; 44,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>34,72; 40,94</t>
+          <t>34,94; 41,23</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>30,14; 36,69</t>
+          <t>30,15; 36,79</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>26,94; 32,52</t>
+          <t>26,74; 32,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>38,86; 44,34</t>
+          <t>39,4; 44,69</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40,73; 44,53</t>
+          <t>40,72; 44,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>42,44; 46,07</t>
+          <t>42,01; 45,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37,53; 40,82</t>
+          <t>37,28; 40,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>45,55; 61,58</t>
+          <t>43,79; 47,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>55,21; 58,68</t>
+          <t>55,26; 58,74</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>52,65; 56,03</t>
+          <t>52,49; 55,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,08; 49,49</t>
+          <t>46,22; 49,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51,09; 62,57</t>
+          <t>51,37; 54,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>48,72; 51,17</t>
+          <t>48,72; 51,26</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>48,03; 50,42</t>
+          <t>47,98; 50,45</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42,4; 44,67</t>
+          <t>42,41; 44,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>48,97; 58,49</t>
+          <t>48,26; 50,53</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346564</t>
+          <t>376873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>595168</t>
+          <t>641750</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>941732</t>
+          <t>1018623</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>612280; 677562</t>
+          <t>614906; 673831</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>601221; 659035</t>
+          <t>598933; 659447</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>433446; 488599</t>
+          <t>435784; 489203</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>324082; 366462</t>
+          <t>353127; 400105</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>966191; 1025466</t>
+          <t>964668; 1026594</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>953302; 1019602</t>
+          <t>948579; 1018322</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>694664; 753638</t>
+          <t>692969; 750073</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>575462; 613727</t>
+          <t>620967; 661754</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1592478; 1687401</t>
+          <t>1597746; 1684110</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1570548; 1661291</t>
+          <t>1569818; 1657302</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1143882; 1224535</t>
+          <t>1141243; 1219500</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>914318; 970138</t>
+          <t>986725; 1048870</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1093457</t>
+          <t>921658</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1122737</t>
+          <t>1013901</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2216194</t>
+          <t>1935560</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>531527; 610934</t>
+          <t>533371; 610480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>688590; 778597</t>
+          <t>685840; 774212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>674921; 762029</t>
+          <t>674469; 765068</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>936713; 1488324</t>
+          <t>865577; 982550</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>683709; 760617</t>
+          <t>678597; 760353</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>725513; 810901</t>
+          <t>727556; 810944</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>739616; 829901</t>
+          <t>738405; 829311</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>981467; 1421310</t>
+          <t>969832; 1055764</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1234878; 1347323</t>
+          <t>1237850; 1350251</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1440591; 1562730</t>
+          <t>1435478; 1557324</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1435426; 1564096</t>
+          <t>1434512; 1566207</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1958992; 2644860</t>
+          <t>1863730; 2004835</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>273520</t>
+          <t>297637</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>268271</t>
+          <t>305178</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>541791</t>
+          <t>602815</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>156720; 202473</t>
+          <t>159187; 202838</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>122867; 165791</t>
+          <t>123103; 165546</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>120521; 164202</t>
+          <t>118098; 159436</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>246001; 300571</t>
+          <t>269853; 327084</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>187883; 233104</t>
+          <t>187727; 232322</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>152038; 194003</t>
+          <t>148710; 193442</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>161382; 207210</t>
+          <t>161443; 207342</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>247487; 290458</t>
+          <t>278558; 327112</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>356904; 420836</t>
+          <t>359100; 423736</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>283238; 344793</t>
+          <t>283391; 345770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>295259; 356452</t>
+          <t>293106; 355783</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>506007; 577299</t>
+          <t>567747; 644020</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1713541</t>
+          <t>1596169</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1986176</t>
+          <t>1960829</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3699717</t>
+          <t>3556998</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1334686; 1458948</t>
+          <t>1334087; 1455877</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1451499; 1575620</t>
+          <t>1436590; 1562202</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1267604; 1378641</t>
+          <t>1259077; 1378645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1565279; 2116264</t>
+          <t>1534399; 1657959</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1865497; 1982855</t>
+          <t>1867507; 1984856</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1871305; 1991580</t>
+          <t>1865451; 1984915</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1627701; 1747954</t>
+          <t>1632621; 1754400</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1857136; 2274429</t>
+          <t>1905289; 2015972</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3242413; 3406066</t>
+          <t>3242541; 3411872</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3349829; 3516048</t>
+          <t>3345803; 3518654</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2929660; 3086588</t>
+          <t>2930164; 3088141</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3463289; 4136424</t>
+          <t>3480512; 3644232</t>
         </is>
       </c>
     </row>
